--- a/lab/ornek/fx-blotter-ornek.xlsx
+++ b/lab/ornek/fx-blotter-ornek.xlsx
@@ -91,7 +91,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">ÖRNEK BANKA A.Ş. HAZİNE - FX İŞLEM LİSTESİ (SENTETİK ÖRNEK, GERÇEK VERİ DEĞİLDİR)</t>
+          <t xml:space="preserve">ÖRNEK BANKA A.Ş. HAZİNE - FX İŞLEM LİSTESİ (ÖRNEK)</t>
         </is>
       </c>
     </row>
